--- a/test-cases/product-details-test-cases.xlsx
+++ b/test-cases/product-details-test-cases.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17580" activeTab="1"/>
+    <workbookView windowHeight="17580"/>
   </bookViews>
   <sheets>
     <sheet name="Test Cases" sheetId="2" r:id="rId1"/>
@@ -28,12 +28,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="34">
   <si>
     <t>TC ID</t>
   </si>
   <si>
     <t>Title</t>
+  </si>
+  <si>
+    <t>Test Type</t>
   </si>
   <si>
     <t>Precondition</t>
@@ -1357,18 +1360,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G47"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
+  <dimension ref="A1:H47"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="18.375" customWidth="1"/>
     <col min="2" max="2" width="38.875" customWidth="1"/>
-    <col min="3" max="3" width="33.625" customWidth="1"/>
-    <col min="4" max="4" width="36.25" customWidth="1"/>
-    <col min="5" max="5" width="59.375" customWidth="1"/>
-    <col min="6" max="6" width="41" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="33.625" customWidth="1"/>
+    <col min="5" max="5" width="36.25" customWidth="1"/>
+    <col min="6" max="6" width="59.375" customWidth="1"/>
+    <col min="7" max="7" width="41" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" spans="1:7">
+    <row r="1" ht="15.75" spans="1:8">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -1390,17 +1394,18 @@
       <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" ht="91" customHeight="1" spans="1:7">
+      <c r="H1" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" ht="91" customHeight="1" spans="1:8">
       <c r="A2" s="9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
         <v>10</v>
       </c>
@@ -1410,57 +1415,62 @@
       <c r="F2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" ht="157" customHeight="1" spans="1:7">
+      <c r="H2" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" ht="157" customHeight="1" spans="1:8">
       <c r="A3" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" ht="129" customHeight="1" spans="1:7">
+      <c r="G3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" ht="129" customHeight="1" spans="1:8">
       <c r="A4" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" ht="63" customHeight="1" spans="1:7">
+      <c r="G4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" ht="63" customHeight="1" spans="1:8">
       <c r="A5" s="12"/>
       <c r="B5" s="12"/>
       <c r="C5" s="12"/>
@@ -1468,8 +1478,9 @@
       <c r="E5" s="12"/>
       <c r="F5" s="12"/>
       <c r="G5" s="12"/>
-    </row>
-    <row r="6" ht="72" customHeight="1" spans="1:7">
+      <c r="H5" s="12"/>
+    </row>
+    <row r="6" ht="72" customHeight="1" spans="1:8">
       <c r="A6" s="12"/>
       <c r="B6" s="12"/>
       <c r="C6" s="12"/>
@@ -1477,8 +1488,9 @@
       <c r="E6" s="12"/>
       <c r="F6" s="12"/>
       <c r="G6" s="12"/>
-    </row>
-    <row r="7" ht="72" customHeight="1" spans="1:7">
+      <c r="H6" s="12"/>
+    </row>
+    <row r="7" ht="72" customHeight="1" spans="1:8">
       <c r="A7" s="12"/>
       <c r="B7" s="12"/>
       <c r="C7" s="12"/>
@@ -1486,8 +1498,9 @@
       <c r="E7" s="12"/>
       <c r="F7" s="12"/>
       <c r="G7" s="12"/>
-    </row>
-    <row r="8" ht="61" customHeight="1" spans="1:7">
+      <c r="H7" s="12"/>
+    </row>
+    <row r="8" ht="61" customHeight="1" spans="1:8">
       <c r="A8" s="12"/>
       <c r="B8" s="12"/>
       <c r="C8" s="12"/>
@@ -1495,8 +1508,9 @@
       <c r="E8" s="12"/>
       <c r="F8" s="12"/>
       <c r="G8" s="12"/>
-    </row>
-    <row r="9" spans="1:7">
+      <c r="H8" s="12"/>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="12"/>
       <c r="B9" s="12"/>
       <c r="C9" s="12"/>
@@ -1504,8 +1518,9 @@
       <c r="E9" s="12"/>
       <c r="F9" s="12"/>
       <c r="G9" s="12"/>
-    </row>
-    <row r="10" spans="1:7">
+      <c r="H9" s="12"/>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="12"/>
       <c r="B10" s="12"/>
       <c r="C10" s="12"/>
@@ -1513,8 +1528,9 @@
       <c r="E10" s="12"/>
       <c r="F10" s="12"/>
       <c r="G10" s="12"/>
-    </row>
-    <row r="11" spans="1:7">
+      <c r="H10" s="12"/>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="12"/>
       <c r="B11" s="12"/>
       <c r="C11" s="12"/>
@@ -1522,8 +1538,9 @@
       <c r="E11" s="12"/>
       <c r="F11" s="12"/>
       <c r="G11" s="12"/>
-    </row>
-    <row r="12" spans="1:7">
+      <c r="H11" s="12"/>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" s="12"/>
       <c r="B12" s="12"/>
       <c r="C12" s="12"/>
@@ -1531,8 +1548,9 @@
       <c r="E12" s="12"/>
       <c r="F12" s="12"/>
       <c r="G12" s="12"/>
-    </row>
-    <row r="13" spans="1:7">
+      <c r="H12" s="12"/>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="12"/>
       <c r="B13" s="12"/>
       <c r="C13" s="12"/>
@@ -1540,8 +1558,9 @@
       <c r="E13" s="12"/>
       <c r="F13" s="12"/>
       <c r="G13" s="12"/>
-    </row>
-    <row r="14" spans="1:7">
+      <c r="H13" s="12"/>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" s="12"/>
       <c r="B14" s="12"/>
       <c r="C14" s="12"/>
@@ -1549,8 +1568,9 @@
       <c r="E14" s="12"/>
       <c r="F14" s="12"/>
       <c r="G14" s="12"/>
-    </row>
-    <row r="15" spans="1:7">
+      <c r="H14" s="12"/>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" s="12"/>
       <c r="B15" s="12"/>
       <c r="C15" s="12"/>
@@ -1558,8 +1578,9 @@
       <c r="E15" s="12"/>
       <c r="F15" s="12"/>
       <c r="G15" s="12"/>
-    </row>
-    <row r="16" spans="1:7">
+      <c r="H15" s="12"/>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" s="12"/>
       <c r="B16" s="12"/>
       <c r="C16" s="12"/>
@@ -1567,8 +1588,9 @@
       <c r="E16" s="12"/>
       <c r="F16" s="12"/>
       <c r="G16" s="12"/>
-    </row>
-    <row r="17" spans="1:7">
+      <c r="H16" s="12"/>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" s="12"/>
       <c r="B17" s="12"/>
       <c r="C17" s="12"/>
@@ -1576,8 +1598,9 @@
       <c r="E17" s="12"/>
       <c r="F17" s="12"/>
       <c r="G17" s="12"/>
-    </row>
-    <row r="18" spans="1:7">
+      <c r="H17" s="12"/>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" s="12"/>
       <c r="B18" s="12"/>
       <c r="C18" s="12"/>
@@ -1585,17 +1608,19 @@
       <c r="E18" s="12"/>
       <c r="F18" s="12"/>
       <c r="G18" s="12"/>
-    </row>
-    <row r="19" spans="1:7">
+      <c r="H18" s="12"/>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" s="12"/>
       <c r="B19" s="12"/>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="7"/>
       <c r="G19" s="12"/>
-    </row>
-    <row r="20" spans="1:7">
+      <c r="H19" s="12"/>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" s="12"/>
       <c r="B20" s="12"/>
       <c r="C20" s="12"/>
@@ -1603,8 +1628,9 @@
       <c r="E20" s="12"/>
       <c r="F20" s="12"/>
       <c r="G20" s="12"/>
-    </row>
-    <row r="21" spans="1:7">
+      <c r="H20" s="12"/>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" s="12"/>
       <c r="B21" s="12"/>
       <c r="C21" s="12"/>
@@ -1612,8 +1638,9 @@
       <c r="E21" s="12"/>
       <c r="F21" s="12"/>
       <c r="G21" s="12"/>
-    </row>
-    <row r="22" spans="1:7">
+      <c r="H21" s="12"/>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" s="12"/>
       <c r="B22" s="12"/>
       <c r="C22" s="12"/>
@@ -1621,8 +1648,9 @@
       <c r="E22" s="12"/>
       <c r="F22" s="12"/>
       <c r="G22" s="12"/>
-    </row>
-    <row r="23" spans="1:7">
+      <c r="H22" s="12"/>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" s="12"/>
       <c r="B23" s="12"/>
       <c r="C23" s="12"/>
@@ -1630,8 +1658,9 @@
       <c r="E23" s="12"/>
       <c r="F23" s="12"/>
       <c r="G23" s="12"/>
-    </row>
-    <row r="24" spans="1:7">
+      <c r="H23" s="12"/>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" s="12"/>
       <c r="B24" s="12"/>
       <c r="C24" s="12"/>
@@ -1639,8 +1668,9 @@
       <c r="E24" s="12"/>
       <c r="F24" s="12"/>
       <c r="G24" s="12"/>
-    </row>
-    <row r="25" spans="1:7">
+      <c r="H24" s="12"/>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" s="12"/>
       <c r="B25" s="12"/>
       <c r="C25" s="12"/>
@@ -1648,8 +1678,9 @@
       <c r="E25" s="12"/>
       <c r="F25" s="12"/>
       <c r="G25" s="12"/>
-    </row>
-    <row r="26" spans="1:7">
+      <c r="H25" s="12"/>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" s="12"/>
       <c r="B26" s="12"/>
       <c r="C26" s="12"/>
@@ -1657,8 +1688,9 @@
       <c r="E26" s="12"/>
       <c r="F26" s="12"/>
       <c r="G26" s="12"/>
-    </row>
-    <row r="27" spans="1:7">
+      <c r="H26" s="12"/>
+    </row>
+    <row r="27" spans="1:8">
       <c r="A27" s="12"/>
       <c r="B27" s="12"/>
       <c r="C27" s="12"/>
@@ -1666,8 +1698,9 @@
       <c r="E27" s="12"/>
       <c r="F27" s="12"/>
       <c r="G27" s="12"/>
-    </row>
-    <row r="28" spans="1:7">
+      <c r="H27" s="12"/>
+    </row>
+    <row r="28" spans="1:8">
       <c r="A28" s="12"/>
       <c r="B28" s="12"/>
       <c r="C28" s="12"/>
@@ -1675,8 +1708,9 @@
       <c r="E28" s="12"/>
       <c r="F28" s="12"/>
       <c r="G28" s="12"/>
-    </row>
-    <row r="29" spans="1:7">
+      <c r="H28" s="12"/>
+    </row>
+    <row r="29" spans="1:8">
       <c r="A29" s="12"/>
       <c r="B29" s="12"/>
       <c r="C29" s="12"/>
@@ -1684,8 +1718,9 @@
       <c r="E29" s="12"/>
       <c r="F29" s="12"/>
       <c r="G29" s="12"/>
-    </row>
-    <row r="30" spans="1:7">
+      <c r="H29" s="12"/>
+    </row>
+    <row r="30" spans="1:8">
       <c r="A30" s="12"/>
       <c r="B30" s="12"/>
       <c r="C30" s="12"/>
@@ -1693,8 +1728,9 @@
       <c r="E30" s="12"/>
       <c r="F30" s="12"/>
       <c r="G30" s="12"/>
-    </row>
-    <row r="31" spans="1:7">
+      <c r="H30" s="12"/>
+    </row>
+    <row r="31" spans="1:8">
       <c r="A31" s="12"/>
       <c r="B31" s="12"/>
       <c r="C31" s="12"/>
@@ -1702,8 +1738,9 @@
       <c r="E31" s="12"/>
       <c r="F31" s="12"/>
       <c r="G31" s="12"/>
-    </row>
-    <row r="32" spans="1:7">
+      <c r="H31" s="12"/>
+    </row>
+    <row r="32" spans="1:8">
       <c r="A32" s="12"/>
       <c r="B32" s="12"/>
       <c r="C32" s="12"/>
@@ -1711,8 +1748,9 @@
       <c r="E32" s="12"/>
       <c r="F32" s="12"/>
       <c r="G32" s="12"/>
-    </row>
-    <row r="33" spans="1:7">
+      <c r="H32" s="12"/>
+    </row>
+    <row r="33" spans="1:8">
       <c r="A33" s="12"/>
       <c r="B33" s="12"/>
       <c r="C33" s="12"/>
@@ -1720,8 +1758,9 @@
       <c r="E33" s="12"/>
       <c r="F33" s="12"/>
       <c r="G33" s="12"/>
-    </row>
-    <row r="34" spans="1:7">
+      <c r="H33" s="12"/>
+    </row>
+    <row r="34" spans="1:8">
       <c r="A34" s="12"/>
       <c r="B34" s="12"/>
       <c r="C34" s="12"/>
@@ -1729,8 +1768,9 @@
       <c r="E34" s="12"/>
       <c r="F34" s="12"/>
       <c r="G34" s="12"/>
-    </row>
-    <row r="35" spans="1:7">
+      <c r="H34" s="12"/>
+    </row>
+    <row r="35" spans="1:8">
       <c r="A35" s="12"/>
       <c r="B35" s="12"/>
       <c r="C35" s="12"/>
@@ -1738,8 +1778,9 @@
       <c r="E35" s="12"/>
       <c r="F35" s="12"/>
       <c r="G35" s="12"/>
-    </row>
-    <row r="36" spans="1:7">
+      <c r="H35" s="12"/>
+    </row>
+    <row r="36" spans="1:8">
       <c r="A36" s="12"/>
       <c r="B36" s="12"/>
       <c r="C36" s="12"/>
@@ -1747,8 +1788,9 @@
       <c r="E36" s="12"/>
       <c r="F36" s="12"/>
       <c r="G36" s="12"/>
-    </row>
-    <row r="37" spans="1:7">
+      <c r="H36" s="12"/>
+    </row>
+    <row r="37" spans="1:8">
       <c r="A37" s="12"/>
       <c r="B37" s="12"/>
       <c r="C37" s="12"/>
@@ -1756,8 +1798,9 @@
       <c r="E37" s="12"/>
       <c r="F37" s="12"/>
       <c r="G37" s="12"/>
-    </row>
-    <row r="38" spans="1:7">
+      <c r="H37" s="12"/>
+    </row>
+    <row r="38" spans="1:8">
       <c r="A38" s="12"/>
       <c r="B38" s="12"/>
       <c r="C38" s="12"/>
@@ -1765,8 +1808,9 @@
       <c r="E38" s="12"/>
       <c r="F38" s="12"/>
       <c r="G38" s="12"/>
-    </row>
-    <row r="39" spans="1:7">
+      <c r="H38" s="12"/>
+    </row>
+    <row r="39" spans="1:8">
       <c r="A39" s="12"/>
       <c r="B39" s="12"/>
       <c r="C39" s="12"/>
@@ -1774,8 +1818,9 @@
       <c r="E39" s="12"/>
       <c r="F39" s="12"/>
       <c r="G39" s="12"/>
-    </row>
-    <row r="40" spans="1:7">
+      <c r="H39" s="12"/>
+    </row>
+    <row r="40" spans="1:8">
       <c r="A40" s="12"/>
       <c r="B40" s="12"/>
       <c r="C40" s="12"/>
@@ -1783,8 +1828,9 @@
       <c r="E40" s="12"/>
       <c r="F40" s="12"/>
       <c r="G40" s="12"/>
-    </row>
-    <row r="41" spans="1:7">
+      <c r="H40" s="12"/>
+    </row>
+    <row r="41" spans="1:8">
       <c r="A41" s="12"/>
       <c r="B41" s="12"/>
       <c r="C41" s="12"/>
@@ -1792,8 +1838,9 @@
       <c r="E41" s="12"/>
       <c r="F41" s="12"/>
       <c r="G41" s="12"/>
-    </row>
-    <row r="42" spans="1:7">
+      <c r="H41" s="12"/>
+    </row>
+    <row r="42" spans="1:8">
       <c r="A42" s="12"/>
       <c r="B42" s="12"/>
       <c r="C42" s="12"/>
@@ -1801,8 +1848,9 @@
       <c r="E42" s="12"/>
       <c r="F42" s="12"/>
       <c r="G42" s="12"/>
-    </row>
-    <row r="43" spans="1:7">
+      <c r="H42" s="12"/>
+    </row>
+    <row r="43" spans="1:8">
       <c r="A43" s="12"/>
       <c r="B43" s="12"/>
       <c r="C43" s="12"/>
@@ -1810,8 +1858,9 @@
       <c r="E43" s="12"/>
       <c r="F43" s="12"/>
       <c r="G43" s="12"/>
-    </row>
-    <row r="44" spans="1:7">
+      <c r="H43" s="12"/>
+    </row>
+    <row r="44" spans="1:8">
       <c r="A44" s="12"/>
       <c r="B44" s="12"/>
       <c r="C44" s="12"/>
@@ -1819,8 +1868,9 @@
       <c r="E44" s="12"/>
       <c r="F44" s="12"/>
       <c r="G44" s="12"/>
-    </row>
-    <row r="45" spans="1:7">
+      <c r="H44" s="12"/>
+    </row>
+    <row r="45" spans="1:8">
       <c r="A45" s="12"/>
       <c r="B45" s="12"/>
       <c r="C45" s="12"/>
@@ -1828,8 +1878,9 @@
       <c r="E45" s="12"/>
       <c r="F45" s="12"/>
       <c r="G45" s="12"/>
-    </row>
-    <row r="46" spans="1:7">
+      <c r="H45" s="12"/>
+    </row>
+    <row r="46" spans="1:8">
       <c r="A46" s="12"/>
       <c r="B46" s="12"/>
       <c r="C46" s="12"/>
@@ -1837,8 +1888,9 @@
       <c r="E46" s="12"/>
       <c r="F46" s="12"/>
       <c r="G46" s="12"/>
-    </row>
-    <row r="47" spans="1:7">
+      <c r="H46" s="12"/>
+    </row>
+    <row r="47" spans="1:8">
       <c r="A47" s="12"/>
       <c r="B47" s="12"/>
       <c r="C47" s="12"/>
@@ -1846,6 +1898,7 @@
       <c r="E47" s="12"/>
       <c r="F47" s="12"/>
       <c r="G47" s="12"/>
+      <c r="H47" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1872,33 +1925,33 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" ht="66" customHeight="1" spans="1:7">
       <c r="A2" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="5">
@@ -1907,16 +1960,16 @@
     </row>
     <row r="3" ht="96" customHeight="1" spans="1:7">
       <c r="A3" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>30</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>29</v>
       </c>
       <c r="E3" s="4"/>
       <c r="F3" s="5">
@@ -1925,16 +1978,16 @@
     </row>
     <row r="4" ht="132" customHeight="1" spans="1:7">
       <c r="A4" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="5">

--- a/test-cases/product-details-test-cases.xlsx
+++ b/test-cases/product-details-test-cases.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17580"/>
+    <workbookView windowWidth="25800" windowHeight="17580"/>
   </bookViews>
   <sheets>
     <sheet name="Test Cases" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="36">
   <si>
     <t>TC ID</t>
   </si>
@@ -58,6 +58,9 @@
   </si>
   <si>
     <t>Verify Product Details Page Opens</t>
+  </si>
+  <si>
+    <t>Positive</t>
   </si>
   <si>
     <t>ผู้ใช้ Login สำเร็จ และอยู่หน้า Products</t>
@@ -76,7 +79,7 @@
 3. ไม่มี Error หรือหน้าว่าง</t>
   </si>
   <si>
-    <t>High</t>
+    <t>Medium</t>
   </si>
   <si>
     <t>TC-DETAIL-002</t>
@@ -96,7 +99,7 @@
 2. ชื่อสินค้าและคำอธิบายไม่เป็นค่าว่าง
 3. แสดงราคาที่มีค่าตัวเลขอ่านได้
 4. รูปภาพปรากฏและโหลดสำเร็จ ไม่ใช่ภาพเสีย
-2. ไม่มี Error หรือหน้าว่าง</t>
+5. ไม่มี Error หรือหน้าว่าง</t>
   </si>
   <si>
     <t>TC-DETAIL-003</t>
@@ -114,6 +117,9 @@
 2. คำอธิบายสินค้าในหน้า Product Details ตรงกับหน้า Products
 3. ราคาสินค้าในหน้า Product Details ตรงกับหน้า Products
 4. รูปภาพในหน้า Product Details เป็นรูปของสินค้ารายการเดียวกันกับหน้า Products</t>
+  </si>
+  <si>
+    <t>High</t>
   </si>
   <si>
     <t>Actual Result</t>
@@ -1370,6 +1376,7 @@
     <col min="5" max="5" width="36.25" customWidth="1"/>
     <col min="6" max="6" width="59.375" customWidth="1"/>
     <col min="7" max="7" width="41" customWidth="1"/>
+    <col min="8" max="8" width="12.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" spans="1:8">
@@ -1405,69 +1412,75 @@
       <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="2"/>
+      <c r="C2" s="10" t="s">
+        <v>10</v>
+      </c>
       <c r="D2" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" ht="157" customHeight="1" spans="1:8">
       <c r="A3" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="10" t="s">
         <v>15</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="10" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="4" ht="129" customHeight="1" spans="1:8">
       <c r="A4" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="4"/>
+        <v>21</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="D4" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" ht="63" customHeight="1" spans="1:8">
@@ -1925,19 +1938,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" ht="66" customHeight="1" spans="1:7">
@@ -1945,13 +1958,13 @@
         <v>8</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="5">
@@ -1960,16 +1973,16 @@
     </row>
     <row r="3" ht="96" customHeight="1" spans="1:7">
       <c r="A3" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>29</v>
-      </c>
       <c r="D3" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E3" s="4"/>
       <c r="F3" s="5">
@@ -1978,16 +1991,16 @@
     </row>
     <row r="4" ht="132" customHeight="1" spans="1:7">
       <c r="A4" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="5">

--- a/test-cases/product-details-test-cases.xlsx
+++ b/test-cases/product-details-test-cases.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="96">
   <si>
     <t>SAUCEDEMO  /  PRODUCT DETAILS</t>
   </si>
@@ -148,7 +148,34 @@
     <t>Check the destination page and its content.</t>
   </si>
   <si>
-    <t>The page shows "Sauce Labs Backpack" and is neither blank nor an error page.</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D3348"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>The page shows "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF1D3348"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Sauce Labs Backpack</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D3348"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>" and is neither blank nor an error page.</t>
+    </r>
   </si>
   <si>
     <t>Click Sauce Labs Backpack to open its Product Details page.</t>
@@ -241,6 +268,9 @@
     <t>MANUAL QA TEST DOCUMENTATION   •   TEST EXECUTION RESULTS</t>
   </si>
   <si>
+    <t>Evidence screenshots are grouped by Test Case ID, not individually mapped to each Actual Result entry. One screenshot may support multiple observations.</t>
+  </si>
+  <si>
     <t>Actual Result</t>
   </si>
   <si>
@@ -259,8 +289,7 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>1. The Product Details page opened at https://www.saucedemo.com/inventory-item.html?id=4.
-2. The page displayed "Sauce Labs Backpack" and was neither blank nor an error page.</t>
+    <t>1. The Product Details page opened at https://www.saucedemo.com/inventory-item.html?id=4.</t>
   </si>
   <si>
     <t>PASS</t>
@@ -272,29 +301,76 @@
     <t>Shared evidence: BACKPACK_LISTING.png and BACKPACK_DETAILS.png support multiple Backpack detail checks.</t>
   </si>
   <si>
-    <t>1. The page displayed the product name, description, price ($29.99), and product image.
-2. The name and description were non-empty, the price was readable, and the product image appeared.</t>
-  </si>
-  <si>
-    <t>1. The Product Details page matched the Products page for the Sauce Labs Backpack name, description, price ($29.99), and product image.</t>
-  </si>
-  <si>
-    <t>1. https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/product-details/BACKPACK_LISTING.png
-2. https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/product-details/BACKPACK_DETAILS.png</t>
-  </si>
-  <si>
-    <t>1. The Sauce Labs Backpack was displayed on the Products page.
-2. The Product Details page opened and displayed the correct product name, price ($29.99), and Add to cart button.
-3. After clicking Add to cart, the button changed to Remove.
-4. The cart badge displayed 1, confirming that the selected product was added.
-5. The Shopping Cart displayed one Sauce Labs Backpack with quantity 1 and price $29.99.</t>
-  </si>
-  <si>
-    <t>1. https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/product-details/TC-DETAIL-004_01_PRODUCTS.png
-2. https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/product-details/TC-DETAIL-004_02_DETAILS_BEFORE.png
-3. https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/product-details/TC-DETAIL-004_03_DETAILS_AFTER.png
-4. https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/product-details/TC-DETAIL-004_04_BADGE.png
-5. https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/product-details/TC-DETAIL-004_05_CART.png</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D3348"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2. The page displayed "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF1D3348"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Sauce Labs Backpack</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D3348"/>
+        <rFont val="Aptos"/>
+        <charset val="134"/>
+      </rPr>
+      <t>" and was neither blank nor an error page.</t>
+    </r>
+  </si>
+  <si>
+    <t>1. The page displayed the product name, description, price ($29.99), and product image.</t>
+  </si>
+  <si>
+    <t>2. The name and description were non-empty, the price was readable, and the product image appeared.</t>
+  </si>
+  <si>
+    <t>The Product Details page matched the Products page for the Sauce Labs Backpack name, description, price ($29.99), and product image.</t>
+  </si>
+  <si>
+    <t>https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/product-details/BACKPACK_LISTING.png</t>
+  </si>
+  <si>
+    <t>1. The Sauce Labs Backpack was displayed on the Products page.</t>
+  </si>
+  <si>
+    <t>https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/product-details/TC-DETAIL-004_01_PRODUCTS.png</t>
+  </si>
+  <si>
+    <t>2. The Product Details page opened and displayed the correct product name, price ($29.99), and Add to cart button.</t>
+  </si>
+  <si>
+    <t>https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/product-details/TC-DETAIL-004_02_DETAILS_BEFORE.png</t>
+  </si>
+  <si>
+    <t>3. After clicking Add to cart, the button changed to Remove.</t>
+  </si>
+  <si>
+    <t>https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/product-details/TC-DETAIL-004_03_DETAILS_AFTER.png</t>
+  </si>
+  <si>
+    <t>4. The cart badge displayed 1, confirming that the selected product was added.</t>
+  </si>
+  <si>
+    <t>https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/product-details/TC-DETAIL-004_04_BADGE.png</t>
+  </si>
+  <si>
+    <t>5. The Shopping Cart displayed one Sauce Labs Backpack with quantity 1 and price $29.99.</t>
+  </si>
+  <si>
+    <t>https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/product-details/TC-DETAIL-004_05_CART.png</t>
   </si>
 </sst>
 </file>
@@ -308,7 +384,7 @@
     <numFmt numFmtId="179" formatCode="_-&quot;฿&quot;* #,##0_-;\-&quot;฿&quot;* #,##0_-;_-&quot;฿&quot;* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="180" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -336,6 +412,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF002060"/>
+      <name val="Carlito"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="10"/>
       <color theme="3" tint="0.1"/>
@@ -357,12 +439,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -377,6 +453,12 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
@@ -485,6 +567,13 @@
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF1D3348"/>
+      <name val="Aptos"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="39">
     <fill>
@@ -716,7 +805,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -790,16 +879,75 @@
     </border>
     <border>
       <left style="hair">
-        <color rgb="FF303944"/>
+        <color auto="1"/>
       </left>
       <right style="hair">
-        <color rgb="FF303944"/>
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color auto="1"/>
+      </left>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color auto="1"/>
+      </left>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color auto="1"/>
+      </left>
+      <right style="hair">
+        <color auto="1"/>
       </right>
       <top style="hair">
         <color rgb="FF303944"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color rgb="FF303944"/>
+      </left>
+      <right/>
+      <top style="hair">
+        <color rgb="FF303944"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
       <bottom style="hair">
-        <color rgb="FF303944"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -831,6 +979,21 @@
       <top/>
       <bottom style="hair">
         <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color rgb="FF303944"/>
+      </left>
+      <right style="hair">
+        <color rgb="FF303944"/>
+      </right>
+      <top style="hair">
+        <color rgb="FF303944"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="FF303944"/>
       </bottom>
       <diagonal/>
     </border>
@@ -950,16 +1113,13 @@
     <xf numFmtId="179" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="17" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -968,46 +1128,49 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1016,10 +1179,10 @@
     <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1028,10 +1191,10 @@
     <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1040,10 +1203,10 @@
     <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1052,10 +1215,10 @@
     <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1064,10 +1227,10 @@
     <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1076,11 +1239,11 @@
     <xf numFmtId="0" fontId="10" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1103,92 +1266,167 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="6" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="6" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="6" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="6" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="6" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="6" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="11" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="12" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="6" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="6" xfId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="180" fontId="5" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="6" xfId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="5" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="6" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1196,25 +1434,31 @@
     <xf numFmtId="0" fontId="9" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1272,7 +1516,17 @@
   <dxfs count="22">
     <dxf>
       <font>
-        <color theme="9"/>
+        <color theme="5"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0070C0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
       </font>
     </dxf>
     <dxf>
@@ -1282,17 +1536,7 @@
     </dxf>
     <dxf>
       <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0070C0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="5"/>
+        <color theme="9"/>
       </font>
     </dxf>
     <dxf>
@@ -1729,24 +1973,24 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:7">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="28"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="50"/>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:7">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="31"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="52"/>
     </row>
     <row r="3" ht="26" customHeight="1" spans="1:7">
       <c r="A3" s="5" t="s">
@@ -1754,19 +1998,19 @@
       </c>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
-      <c r="D3" s="32" t="s">
+      <c r="D3" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="32"/>
-      <c r="F3" s="33"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="54"/>
     </row>
     <row r="4" ht="11" customHeight="1" spans="1:7">
-      <c r="A4" s="8"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="34"/>
+      <c r="A4" s="55"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="57"/>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:7">
       <c r="A5" s="10" t="s">
@@ -1787,99 +2031,99 @@
       <c r="F5" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="41" t="s">
+      <c r="G5" s="66" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="6" ht="50" customHeight="1" spans="1:7">
-      <c r="A6" s="42" t="s">
+      <c r="A6" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="43" t="s">
+      <c r="B6" s="68" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="44" t="s">
+      <c r="C6" s="69" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="44" t="s">
+      <c r="D6" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="43" t="s">
+      <c r="E6" s="68" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="44" t="s">
+      <c r="F6" s="69" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="45" t="s">
+      <c r="G6" s="70" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="7" ht="50" customHeight="1" spans="1:7">
-      <c r="A7" s="37" t="s">
+      <c r="A7" s="61" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="38" t="s">
+      <c r="C7" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="38" t="s">
+      <c r="D7" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="38" t="s">
+      <c r="F7" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="G7" s="46" t="s">
+      <c r="G7" s="71" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="8" ht="50" customHeight="1" spans="1:7">
-      <c r="A8" s="42" t="s">
+      <c r="A8" s="67" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="43" t="s">
+      <c r="B8" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="44" t="s">
+      <c r="C8" s="69" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="44" t="s">
+      <c r="D8" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="43" t="s">
+      <c r="E8" s="68" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="44" t="s">
+      <c r="F8" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="G8" s="45" t="s">
+      <c r="G8" s="70" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="9" ht="52" customHeight="1" spans="1:7">
-      <c r="A9" s="24" t="s">
+      <c r="A9" s="72" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="25" t="s">
+      <c r="B9" s="73" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="47" t="s">
+      <c r="C9" s="74" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="47" t="s">
+      <c r="D9" s="74" t="s">
         <v>14</v>
       </c>
-      <c r="E9" s="25" t="s">
+      <c r="E9" s="73" t="s">
         <v>26</v>
       </c>
-      <c r="F9" s="47" t="s">
+      <c r="F9" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="G9" s="46" t="s">
+      <c r="G9" s="71" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1914,40 +2158,40 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:5">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="28"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="50"/>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:5">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="31"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="52"/>
     </row>
     <row r="3" ht="26" customHeight="1" spans="1:5">
       <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="6"/>
-      <c r="C3" s="32" t="s">
+      <c r="C3" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="32"/>
-      <c r="E3" s="33"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="54"/>
     </row>
     <row r="4" ht="11" customHeight="1" spans="1:5">
-      <c r="A4" s="8"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="34"/>
+      <c r="A4" s="55"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="57"/>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:5">
       <c r="A5" s="10" t="s">
@@ -1967,10 +2211,10 @@
       </c>
     </row>
     <row r="6" ht="29" customHeight="1" spans="1:5">
-      <c r="A6" s="35" t="s">
+      <c r="A6" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="36">
+      <c r="B6" s="59">
         <v>1</v>
       </c>
       <c r="C6" s="12" t="s">
@@ -1984,8 +2228,8 @@
       </c>
     </row>
     <row r="7" ht="29" customHeight="1" spans="1:5">
-      <c r="A7" s="15"/>
-      <c r="B7" s="36">
+      <c r="A7" s="60"/>
+      <c r="B7" s="59">
         <v>2</v>
       </c>
       <c r="C7" s="12" t="s">
@@ -1999,8 +2243,8 @@
       </c>
     </row>
     <row r="8" ht="42" customHeight="1" spans="1:5">
-      <c r="A8" s="15"/>
-      <c r="B8" s="36">
+      <c r="A8" s="60"/>
+      <c r="B8" s="59">
         <v>3</v>
       </c>
       <c r="C8" s="12" t="s">
@@ -2014,87 +2258,87 @@
       </c>
     </row>
     <row r="9" ht="42" customHeight="1" spans="1:5">
-      <c r="A9" s="37" t="s">
+      <c r="A9" s="61" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="38">
+      <c r="B9" s="62">
         <v>1</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="24" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="10" ht="29" customHeight="1" spans="1:5">
-      <c r="A10" s="21"/>
-      <c r="B10" s="38">
+      <c r="A10" s="63"/>
+      <c r="B10" s="62">
         <v>2</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="E10" s="18" t="s">
+      <c r="E10" s="24" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="11" ht="29" customHeight="1" spans="1:5">
-      <c r="A11" s="21"/>
-      <c r="B11" s="38">
+      <c r="A11" s="63"/>
+      <c r="B11" s="62">
         <v>3</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="D11" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="E11" s="24" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="12" ht="29" customHeight="1" spans="1:5">
-      <c r="A12" s="21"/>
-      <c r="B12" s="38">
+      <c r="A12" s="63"/>
+      <c r="B12" s="62">
         <v>4</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D12" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="E12" s="18" t="s">
+      <c r="E12" s="24" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="13" ht="42" customHeight="1" spans="1:5">
-      <c r="A13" s="21"/>
-      <c r="B13" s="38">
+      <c r="A13" s="63"/>
+      <c r="B13" s="62">
         <v>5</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="D13" s="18" t="s">
+      <c r="D13" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="E13" s="18" t="s">
+      <c r="E13" s="24" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="14" ht="42" customHeight="1" spans="1:5">
-      <c r="A14" s="35" t="s">
+      <c r="A14" s="58" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="36">
+      <c r="B14" s="59">
         <v>1</v>
       </c>
       <c r="C14" s="12" t="s">
@@ -2108,8 +2352,8 @@
       </c>
     </row>
     <row r="15" ht="29" customHeight="1" spans="1:5">
-      <c r="A15" s="15"/>
-      <c r="B15" s="36">
+      <c r="A15" s="60"/>
+      <c r="B15" s="59">
         <v>2</v>
       </c>
       <c r="C15" s="12" t="s">
@@ -2123,8 +2367,8 @@
       </c>
     </row>
     <row r="16" ht="42" customHeight="1" spans="1:5">
-      <c r="A16" s="15"/>
-      <c r="B16" s="36">
+      <c r="A16" s="60"/>
+      <c r="B16" s="59">
         <v>3</v>
       </c>
       <c r="C16" s="12" t="s">
@@ -2138,79 +2382,79 @@
       </c>
     </row>
     <row r="17" ht="43" customHeight="1" spans="1:5">
-      <c r="A17" s="39" t="s">
+      <c r="A17" s="64" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="38">
+      <c r="B17" s="62">
         <v>1</v>
       </c>
-      <c r="C17" s="18" t="s">
+      <c r="C17" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="D17" s="18" t="s">
+      <c r="D17" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="E17" s="18" t="s">
+      <c r="E17" s="24" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="18" ht="38" customHeight="1" spans="1:5">
-      <c r="A18" s="40"/>
-      <c r="B18" s="38">
+      <c r="A18" s="65"/>
+      <c r="B18" s="62">
         <v>2</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="C18" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="D18" s="18" t="s">
+      <c r="D18" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="E18" s="18" t="s">
+      <c r="E18" s="24" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:5">
-      <c r="A19" s="40"/>
-      <c r="B19" s="38">
+      <c r="A19" s="65"/>
+      <c r="B19" s="62">
         <v>3</v>
       </c>
-      <c r="C19" s="18" t="s">
+      <c r="C19" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="D19" s="18" t="s">
+      <c r="D19" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="E19" s="18" t="s">
+      <c r="E19" s="24" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:5">
-      <c r="A20" s="40"/>
-      <c r="B20" s="38">
+      <c r="A20" s="65"/>
+      <c r="B20" s="62">
         <v>4</v>
       </c>
-      <c r="C20" s="18" t="s">
+      <c r="C20" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="D20" s="18" t="s">
+      <c r="D20" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="E20" s="18" t="s">
+      <c r="E20" s="24" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="21" ht="39" customHeight="1" spans="1:5">
-      <c r="A21" s="40"/>
-      <c r="B21" s="38">
+      <c r="A21" s="65"/>
+      <c r="B21" s="62">
         <v>5</v>
       </c>
-      <c r="C21" s="18" t="s">
+      <c r="C21" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="D21" s="18" t="s">
+      <c r="D21" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="E21" s="18" t="s">
+      <c r="E21" s="24" t="s">
         <v>68</v>
       </c>
     </row>
@@ -2233,13 +2477,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="65" customWidth="1"/>
     <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="4" max="4" width="68.375" customWidth="1"/>
+    <col min="4" max="4" width="103.75" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
     <col min="6" max="6" width="20" customWidth="1"/>
     <col min="7" max="7" width="52" customWidth="1"/>
@@ -2281,8 +2525,10 @@
       <c r="F3" s="7"/>
       <c r="G3" s="7"/>
     </row>
-    <row r="4" ht="11" customHeight="1" spans="1:7">
-      <c r="A4" s="8"/>
+    <row r="4" customFormat="1" ht="23" customHeight="1" spans="1:7">
+      <c r="A4" s="8" t="s">
+        <v>70</v>
+      </c>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
@@ -2295,156 +2541,271 @@
         <v>4</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="6" ht="82" customHeight="1" spans="1:7">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" ht="41" customHeight="1" spans="1:7">
       <c r="A6" s="11" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E6" s="15"/>
       <c r="F6" s="16">
         <v>46306</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="G6" s="17" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1" spans="1:7">
+      <c r="A7" s="18"/>
+      <c r="B7" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="C7" s="19"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="21"/>
+      <c r="G7" s="22"/>
+    </row>
+    <row r="8" ht="35" customHeight="1" spans="1:7">
+      <c r="A8" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>78</v>
+      </c>
+      <c r="D8" s="26" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="7" ht="86" customHeight="1" spans="1:7">
-      <c r="A7" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="18" t="s">
+      <c r="E8" s="27"/>
+      <c r="F8" s="28">
+        <v>46306</v>
+      </c>
+      <c r="G8" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="C7" s="19" t="s">
-        <v>77</v>
-      </c>
-      <c r="D7" s="20" t="s">
+    </row>
+    <row r="9" ht="45" customHeight="1" spans="1:7">
+      <c r="A9" s="30"/>
+      <c r="B9" s="31" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9" s="32"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="34"/>
+      <c r="G9" s="35"/>
+    </row>
+    <row r="10" ht="56" customHeight="1" spans="1:7">
+      <c r="A10" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="36" t="s">
+        <v>84</v>
+      </c>
+      <c r="C10" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="E7" s="21"/>
-      <c r="F7" s="22">
+      <c r="D10" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="E10" s="15"/>
+      <c r="F10" s="16">
         <v>46306</v>
       </c>
-      <c r="G7" s="18" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="8" ht="98" customHeight="1" spans="1:7">
-      <c r="A8" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="D8" s="23" t="s">
-        <v>82</v>
-      </c>
-      <c r="E8" s="15"/>
-      <c r="F8" s="16">
-        <v>46306</v>
-      </c>
-      <c r="G8" s="12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="9" ht="249" customHeight="1" spans="1:7">
-      <c r="A9" s="24" t="s">
+      <c r="G10" s="36" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" ht="53" customHeight="1" spans="1:7">
+      <c r="A11" s="37"/>
+      <c r="B11" s="38"/>
+      <c r="C11" s="39"/>
+      <c r="D11" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="E11" s="20"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="40"/>
+    </row>
+    <row r="12" ht="50" customHeight="1" spans="1:7">
+      <c r="A12" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="25" t="s">
-        <v>83</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>77</v>
-      </c>
-      <c r="D9" s="25" t="s">
-        <v>84</v>
-      </c>
-      <c r="E9" s="25"/>
-      <c r="F9" s="16">
+      <c r="B12" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="C12" s="25" t="s">
+        <v>78</v>
+      </c>
+      <c r="D12" s="42" t="s">
+        <v>87</v>
+      </c>
+      <c r="E12" s="43"/>
+      <c r="F12" s="28">
         <v>46311</v>
       </c>
-      <c r="G9" s="25"/>
+      <c r="G12" s="43"/>
+    </row>
+    <row r="13" ht="48" customHeight="1" spans="1:7">
+      <c r="A13" s="44"/>
+      <c r="B13" s="24" t="s">
+        <v>88</v>
+      </c>
+      <c r="C13" s="32"/>
+      <c r="D13" s="45" t="s">
+        <v>89</v>
+      </c>
+      <c r="E13" s="35"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="35"/>
+    </row>
+    <row r="14" ht="48" customHeight="1" spans="1:7">
+      <c r="A14" s="44"/>
+      <c r="B14" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C14" s="32"/>
+      <c r="D14" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="E14" s="35"/>
+      <c r="F14" s="34"/>
+      <c r="G14" s="35"/>
+    </row>
+    <row r="15" ht="48" customHeight="1" spans="1:7">
+      <c r="A15" s="44"/>
+      <c r="B15" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="C15" s="32"/>
+      <c r="D15" s="45" t="s">
+        <v>93</v>
+      </c>
+      <c r="E15" s="35"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="35"/>
+    </row>
+    <row r="16" ht="47" customHeight="1" spans="1:7">
+      <c r="A16" s="46"/>
+      <c r="B16" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="C16" s="47"/>
+      <c r="D16" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="E16" s="48"/>
+      <c r="F16" s="49"/>
+      <c r="G16" s="48"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="28">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="E3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A12:A16"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="C12:C16"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="E12:E16"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="F12:F16"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="G12:G16"/>
   </mergeCells>
-  <conditionalFormatting sqref="C9">
-    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
-      <formula>"PASS"</formula>
+  <conditionalFormatting sqref="C12">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>"NEEDS CLARIFICATION"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
-      <formula>"FAIL"</formula>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>"NOT RUN"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>"BLOCKED"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
-      <formula>"NOT RUN"</formula>
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+      <formula>"FAIL"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+      <formula>"PASS"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C6 C8 C10">
+    <cfRule type="cellIs" dxfId="0" priority="6" operator="equal">
       <formula>"NEEDS CLARIFICATION"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C6:C8">
-    <cfRule type="cellIs" dxfId="0" priority="10" operator="equal">
-      <formula>"PASS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="9" operator="equal">
-      <formula>"FAIL"</formula>
+    <cfRule type="cellIs" dxfId="1" priority="7" operator="equal">
+      <formula>"NOT RUN"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="2" priority="8" operator="equal">
       <formula>"BLOCKED"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="7" operator="equal">
-      <formula>"NOT RUN"</formula>
+    <cfRule type="cellIs" dxfId="3" priority="9" operator="equal">
+      <formula>"FAIL"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
-      <formula>"NEEDS CLARIFICATION"</formula>
+    <cfRule type="cellIs" dxfId="4" priority="10" operator="equal">
+      <formula>"PASS"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="C6:C9">
+    <dataValidation type="list" sqref="C6:C12">
       <formula1>"PASS,FAIL,BLOCKED,NOT RUN,NEEDS CLARIFICATION"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="D8" r:id="rId1" display="1. https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/product-details/BACKPACK_LISTING.png&#10;&#10;2. https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/product-details/BACKPACK_DETAILS.png"/>
-    <hyperlink ref="D7" r:id="rId2" display="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/product-details/BACKPACK_DETAILS.png" tooltip="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/product-details/BACKPACK_DETAILS.png"/>
-    <hyperlink ref="D6" r:id="rId2" display="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/product-details/BACKPACK_DETAILS.png" tooltip="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/product-details/BACKPACK_DETAILS.png"/>
+    <hyperlink ref="D8" r:id="rId1" display="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/product-details/BACKPACK_DETAILS.png" tooltip="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/product-details/BACKPACK_DETAILS.png"/>
+    <hyperlink ref="D6" r:id="rId1" display="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/product-details/BACKPACK_DETAILS.png" tooltip="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/product-details/BACKPACK_DETAILS.png"/>
+    <hyperlink ref="D11" r:id="rId2" display="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/product-details/BACKPACK_LISTING.png" tooltip="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/product-details/BACKPACK_LISTING.png"/>
+    <hyperlink ref="D10" r:id="rId1" display="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/product-details/BACKPACK_DETAILS.png" tooltip="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/product-details/BACKPACK_DETAILS.png"/>
+    <hyperlink ref="D12" r:id="rId3" display="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/product-details/TC-DETAIL-004_01_PRODUCTS.png" tooltip="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/product-details/TC-DETAIL-004_01_PRODUCTS.png"/>
+    <hyperlink ref="D13" r:id="rId4" display="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/product-details/TC-DETAIL-004_02_DETAILS_BEFORE.png" tooltip="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/product-details/TC-DETAIL-004_02_DETAILS_BEFORE.png"/>
+    <hyperlink ref="D14" r:id="rId5" display="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/product-details/TC-DETAIL-004_03_DETAILS_AFTER.png" tooltip="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/product-details/TC-DETAIL-004_03_DETAILS_AFTER.png"/>
+    <hyperlink ref="D15" r:id="rId6" display="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/product-details/TC-DETAIL-004_04_BADGE.png" tooltip="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/product-details/TC-DETAIL-004_04_BADGE.png"/>
+    <hyperlink ref="D16" r:id="rId7" display="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/product-details/TC-DETAIL-004_05_CART.png" tooltip="https://github.com/kritsada-chaisongkram/saucedemo-manual-testing/blob/main/test-evidence/product-details/TC-DETAIL-004_05_CART.png"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
